--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:55</t>
+    <t xml:space="preserve">2026-09-10 01:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:06</t>
+    <t xml:space="preserve">2026-09-18 11:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:12</t>
+    <t xml:space="preserve">2026-09-23 14:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:36</t>
+    <t xml:space="preserve">2026-10-02 15:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2024_biobio.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Chiguayante</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Cañete</t>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Negrete</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:40</t>
+    <t xml:space="preserve">2026-10-04 10:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:25</t>
+    <t xml:space="preserve">2026-10-05 15:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
